--- a/diseases/d120/2005-2009.xlsx
+++ b/diseases/d120/2005-2009.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1895,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2345,9 +2336,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -2789,9 +2777,6 @@
       <c r="O15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -3233,9 +3218,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3659,6 @@
       <c r="O21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -4121,9 +4100,6 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -4565,9 +4541,6 @@
       <c r="O27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -5009,9 +4982,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5453,9 +5423,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5897,9 +5864,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -6341,9 +6305,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -6785,9 +6746,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7181,9 +7139,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7580,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -8069,9 +8021,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8462,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8903,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9401,9 +9344,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -9845,9 +9785,6 @@
       <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -10289,9 +10226,6 @@
       <c r="O65" t="n">
         <v>2</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -10733,9 +10667,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -11177,9 +11108,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11621,9 +11549,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -12065,9 +11990,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12657,9 +12579,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13053,9 +12972,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13201,9 +13117,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14041,9 +13954,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14189,9 +14099,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15029,9 +14936,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15177,9 +15081,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -16017,9 +15918,6 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -16165,9 +16063,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -17005,9 +16900,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -17153,9 +17045,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -17993,9 +17882,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -18141,9 +18027,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -18981,9 +18864,6 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -19129,9 +19009,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -19969,9 +19846,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -20117,9 +19991,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -20957,9 +20828,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -21105,9 +20973,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -21945,9 +21810,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -22093,9 +21955,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -22933,9 +22792,6 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -23081,9 +22937,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -23921,9 +23774,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -24069,9 +23919,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -24909,9 +24756,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.3149462465493702</v>
       </c>
@@ -25305,9 +25149,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -25453,9 +25294,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -26293,9 +26131,6 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -26441,9 +26276,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -27281,9 +27113,6 @@
       <c r="O169" t="n">
         <v>2</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -27429,9 +27258,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -28269,9 +28095,6 @@
       <c r="O175" t="n">
         <v>2</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -28417,9 +28240,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -29257,9 +29077,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -29405,9 +29222,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -30245,9 +30059,6 @@
       <c r="O187" t="n">
         <v>2</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -30393,9 +30204,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -31233,9 +31041,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -31381,9 +31186,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -32221,9 +32023,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -32369,9 +32168,6 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -33209,9 +33005,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -33357,9 +33150,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -34197,9 +33987,6 @@
       <c r="O211" t="n">
         <v>4</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -34345,9 +34132,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -35185,9 +34969,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -35333,9 +35114,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -36173,9 +35951,6 @@
       <c r="O223" t="n">
         <v>3</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -36321,9 +36096,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -37161,9 +36933,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -37557,9 +37326,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -37705,9 +37471,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -38545,9 +38308,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -38693,9 +38453,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -39533,9 +39290,6 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -39681,9 +39435,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -40521,9 +40272,6 @@
       <c r="O249" t="n">
         <v>3</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -40669,9 +40417,6 @@
       <c r="O250" t="n">
         <v>1</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -41509,9 +41254,6 @@
       <c r="O255" t="n">
         <v>3</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -41657,9 +41399,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -42497,9 +42236,6 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -42645,9 +42381,6 @@
       <c r="O262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -43485,9 +43218,6 @@
       <c r="O267" t="n">
         <v>2</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -43633,9 +43363,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -44473,9 +44200,6 @@
       <c r="O273" t="n">
         <v>2</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -44621,9 +44345,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -45461,9 +45182,6 @@
       <c r="O279" t="n">
         <v>1</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -45609,9 +45327,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -46449,9 +46164,6 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -46597,9 +46309,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -47437,9 +47146,6 @@
       <c r="O291" t="n">
         <v>1</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -47585,9 +47291,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -48425,9 +48128,6 @@
       <c r="O297" t="n">
         <v>2</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -48571,9 +48271,6 @@
         <v>0</v>
       </c>
       <c r="O298" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
